--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-LA_ESPERANZA.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-LA_ESPERANZA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -498,7 +498,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -508,7 +508,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -810,7 +810,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1288,7 +1288,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1330,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1578,7 +1578,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1682,7 +1682,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1734,7 +1734,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1838,7 +1838,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1850,7 +1850,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1994,7 +1994,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2098,7 +2098,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2202,7 +2202,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2214,7 +2214,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2370,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2536,7 +2536,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2630,7 +2630,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2682,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2774,7 +2774,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2838,7 +2838,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2848,7 +2848,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2900,7 +2900,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2942,7 +2942,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2994,7 +2994,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3034,7 +3034,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3046,7 +3046,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3150,7 +3150,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3212,7 +3212,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LA_ESPERANZA</t>
+          <t>LA ESPERANZA</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-LA_ESPERANZA.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-LA_ESPERANZA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>EL BUEN PASTOR</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-8.078239999999999</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-79.04235</v>
-      </c>
-      <c r="I2" t="n">
-        <v>360</v>
-      </c>
-      <c r="J2" t="n">
-        <v>23</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-8.07824</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-79.04235</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>SOL NACIENTE</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-8.07921</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-79.04397</v>
-      </c>
-      <c r="I3" t="n">
-        <v>360</v>
-      </c>
-      <c r="J3" t="n">
-        <v>17</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-8.07921</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-79.04397</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>UNIVERSAL SCHOOLS</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-8.085839999999999</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-79.03901999999999</v>
-      </c>
-      <c r="I4" t="n">
-        <v>310</v>
-      </c>
-      <c r="J4" t="n">
-        <v>7</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-8.08584</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-79.03902</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>81758 TELMO HOYLE DE LOS RIOS</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-8.0684</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-79.07595000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>953</v>
-      </c>
-      <c r="J5" t="n">
-        <v>38</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-8.0684</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-79.07595</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>81764 LA CANTERA</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-8.05264</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-79.07451</v>
-      </c>
-      <c r="I6" t="n">
-        <v>754</v>
-      </c>
-      <c r="J6" t="n">
-        <v>34</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-8.05264</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-79.07451</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>ABRAHAM LINCOLN</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-8.049480000000003</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-79.07246000000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>437</v>
-      </c>
-      <c r="J7" t="n">
-        <v>24</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-8.049480000000003</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-79.07246</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>106</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-8.07296</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-79.05986</v>
-      </c>
-      <c r="I8" t="n">
-        <v>226</v>
-      </c>
-      <c r="J8" t="n">
-        <v>10</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-8.07296</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-79.05986</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>1560 JESUS NAZARENO</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-8.08089</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-79.04732</v>
-      </c>
-      <c r="I9" t="n">
-        <v>239</v>
-      </c>
-      <c r="J9" t="n">
-        <v>11</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-8.08089</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-79.04732</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>1574 SANTA VERONICA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-8.081466000000002</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-79.05079000000001</v>
-      </c>
-      <c r="I10" t="n">
-        <v>274</v>
-      </c>
-      <c r="J10" t="n">
-        <v>11</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-8.081466000000002</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-79.05079</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>1576 JERUSALEN</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-8.067970000000003</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-79.054</v>
-      </c>
-      <c r="I11" t="n">
-        <v>393</v>
-      </c>
-      <c r="J11" t="n">
-        <v>13</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-8.067970000000003</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-79.054</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>393</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>1680 DIVINA MISERICORDIA</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-8.07512</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-79.04832</v>
-      </c>
-      <c r="I12" t="n">
-        <v>212</v>
-      </c>
-      <c r="J12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-8.07512</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-79.04832</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>1682 VIRGEN DE FATIMA</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-8.060600000000003</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-79.0544</v>
-      </c>
-      <c r="I13" t="n">
-        <v>275</v>
-      </c>
-      <c r="J13" t="n">
-        <v>10</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-8.060600000000003</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-79.0544</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>2021 SARITA COLONIA</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-8.05533</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-79.05322</v>
-      </c>
-      <c r="I14" t="n">
-        <v>226</v>
-      </c>
-      <c r="J14" t="n">
-        <v>9</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-8.05533</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-79.05322</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>CARLOS MANUEL COX ROSSE</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-8.067909999999999</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-79.05753</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1241</v>
-      </c>
-      <c r="J15" t="n">
-        <v>58</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-8.06791</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-79.05753</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1241</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>80036 SAN MARTIN DE PORRES</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-8.07269</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-79.04401</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1367</v>
-      </c>
-      <c r="J16" t="n">
-        <v>67</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-8.07269</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-79.04401</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>80038 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-8.06649</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-79.04855999999999</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1292</v>
-      </c>
-      <c r="J17" t="n">
-        <v>59</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-8.06649</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-79.04856</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>80039 MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-8.07985</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-79.04161000000001</v>
-      </c>
-      <c r="I18" t="n">
-        <v>444</v>
-      </c>
-      <c r="J18" t="n">
-        <v>18</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-8.07985</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-79.04161</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>80040 DIVINO MAESTRO</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-8.08074</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-79.04684</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1590</v>
-      </c>
-      <c r="J19" t="n">
-        <v>63</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-8.08074</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-79.04684</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1590</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>80041 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-8.082789999999999</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-79.0369</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1059</v>
-      </c>
-      <c r="J20" t="n">
-        <v>42</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-8.08279</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-79.0369</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1059</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>80821 CESAR VALLEJO MENDOZA</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-8.083930000000002</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-79.03413999999999</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1765</v>
-      </c>
-      <c r="J21" t="n">
-        <v>88</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-8.083930000000002</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-79.03414</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1765</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1561,20 +1749,30 @@
           <t>80822 SANTA MARIA DE LA ESPERANZA</t>
         </is>
       </c>
-      <c r="G22" t="n">
-        <v>-8.067399999999999</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-79.05419999999999</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2138</v>
-      </c>
-      <c r="J22" t="n">
-        <v>86</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-8.0674</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-79.0542</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2138</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1613,20 +1811,30 @@
           <t>80829 JOSE OLAYA</t>
         </is>
       </c>
-      <c r="G23" t="n">
-        <v>-8.076700000000002</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-79.04996</v>
-      </c>
-      <c r="I23" t="n">
-        <v>1993</v>
-      </c>
-      <c r="J23" t="n">
-        <v>81</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0</v>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-8.076700000000002</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-79.04996</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1665,20 +1873,30 @@
           <t>81608 SAN JOSE</t>
         </is>
       </c>
-      <c r="G24" t="n">
-        <v>-8.0608</v>
-      </c>
-      <c r="H24" t="n">
-        <v>-79.0551</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1801</v>
-      </c>
-      <c r="J24" t="n">
-        <v>68</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0</v>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-8.0608</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>-79.0551</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1801</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1717,20 +1935,30 @@
           <t>81748</t>
         </is>
       </c>
-      <c r="G25" t="n">
-        <v>-8.067729999999999</v>
-      </c>
-      <c r="H25" t="n">
-        <v>-79.06389</v>
-      </c>
-      <c r="I25" t="n">
-        <v>840</v>
-      </c>
-      <c r="J25" t="n">
-        <v>41</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0</v>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-8.06773</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-79.06389</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1769,20 +1997,30 @@
           <t>81751 DIOS ES AMOR</t>
         </is>
       </c>
-      <c r="G26" t="n">
-        <v>-8.056559999999999</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-79.0531</v>
-      </c>
-      <c r="I26" t="n">
-        <v>1478</v>
-      </c>
-      <c r="J26" t="n">
-        <v>57</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0</v>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-8.05656</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-79.0531</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1478</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1821,20 +2059,30 @@
           <t>81763</t>
         </is>
       </c>
-      <c r="G27" t="n">
-        <v>-8.061780000000002</v>
-      </c>
-      <c r="H27" t="n">
-        <v>-79.04693</v>
-      </c>
-      <c r="I27" t="n">
-        <v>370</v>
-      </c>
-      <c r="J27" t="n">
-        <v>14</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-8.061780000000002</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-79.04693</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1873,20 +2121,30 @@
           <t>2028 LUCERITO DEL AMANECER</t>
         </is>
       </c>
-      <c r="G28" t="n">
-        <v>-8.050090000000003</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-79.05092</v>
-      </c>
-      <c r="I28" t="n">
-        <v>197</v>
-      </c>
-      <c r="J28" t="n">
-        <v>7</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-8.050090000000003</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-79.05092</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1925,20 +2183,30 @@
           <t>MADRE DE CRISTO</t>
         </is>
       </c>
-      <c r="G29" t="n">
-        <v>-8.08009</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-79.04522</v>
-      </c>
-      <c r="I29" t="n">
-        <v>525</v>
-      </c>
-      <c r="J29" t="n">
-        <v>19</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-8.08009</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-79.04522</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1977,20 +2245,30 @@
           <t>1702 SANTISIMO SACRAMENTO</t>
         </is>
       </c>
-      <c r="G30" t="n">
-        <v>-8.08329</v>
-      </c>
-      <c r="H30" t="n">
-        <v>-79.03653</v>
-      </c>
-      <c r="I30" t="n">
-        <v>698</v>
-      </c>
-      <c r="J30" t="n">
-        <v>36</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0</v>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-8.08329</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-79.03653</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>698</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -2029,20 +2307,30 @@
           <t>CRISTO REY</t>
         </is>
       </c>
-      <c r="G31" t="n">
-        <v>-8.07098</v>
-      </c>
-      <c r="H31" t="n">
-        <v>-79.05023</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1037</v>
-      </c>
-      <c r="J31" t="n">
-        <v>36</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0</v>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-8.07098</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-79.05023</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1037</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -2081,20 +2369,30 @@
           <t>FE Y ALEGRIA 36</t>
         </is>
       </c>
-      <c r="G32" t="n">
-        <v>-8.0745</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-79.06180000000001</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1301</v>
-      </c>
-      <c r="J32" t="n">
-        <v>61</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0</v>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-8.0745</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-79.0618</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1301</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -2133,20 +2431,30 @@
           <t>INDOAMERICANO</t>
         </is>
       </c>
-      <c r="G33" t="n">
-        <v>-8.062329999999999</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-79.05275</v>
-      </c>
-      <c r="I33" t="n">
-        <v>225</v>
-      </c>
-      <c r="J33" t="n">
-        <v>18</v>
-      </c>
-      <c r="K33" t="n">
-        <v>3</v>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-8.06233</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-79.05275</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2185,20 +2493,30 @@
           <t>ESTUDIANTES EXCELENTES</t>
         </is>
       </c>
-      <c r="G34" t="n">
-        <v>-8.06227</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-79.05297</v>
-      </c>
-      <c r="I34" t="n">
-        <v>96</v>
-      </c>
-      <c r="J34" t="n">
-        <v>9</v>
-      </c>
-      <c r="K34" t="n">
-        <v>3</v>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-8.06227</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-79.05297</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -2237,20 +2555,30 @@
           <t>AMIGOS DE JESUS</t>
         </is>
       </c>
-      <c r="G35" t="n">
-        <v>-8.0542</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-79.05319</v>
-      </c>
-      <c r="I35" t="n">
-        <v>474</v>
-      </c>
-      <c r="J35" t="n">
-        <v>33</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-8.0542</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-79.05319</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>474</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -2289,20 +2617,30 @@
           <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
-      <c r="G36" t="n">
-        <v>-8.07479208879985</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-79.0506266257255</v>
-      </c>
-      <c r="I36" t="n">
-        <v>329</v>
-      </c>
-      <c r="J36" t="n">
-        <v>20</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-8.07479208879985</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-79.0506266257255</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -2341,20 +2679,30 @@
           <t>DOS DE MAYO</t>
         </is>
       </c>
-      <c r="G37" t="n">
-        <v>-8.08042</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-79.04102</v>
-      </c>
-      <c r="I37" t="n">
-        <v>392</v>
-      </c>
-      <c r="J37" t="n">
-        <v>20</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-8.08042</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-79.04102</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>392</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -2393,20 +2741,30 @@
           <t>MARIANO MELGAR</t>
         </is>
       </c>
-      <c r="G38" t="n">
-        <v>-8.06734</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-79.0586</v>
-      </c>
-      <c r="I38" t="n">
-        <v>319</v>
-      </c>
-      <c r="J38" t="n">
-        <v>21</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-8.06734</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-79.0586</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -2445,20 +2803,30 @@
           <t>LIBERTAD</t>
         </is>
       </c>
-      <c r="G39" t="n">
-        <v>-8.079789999999999</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-79.04604</v>
-      </c>
-      <c r="I39" t="n">
-        <v>408</v>
-      </c>
-      <c r="J39" t="n">
-        <v>22</v>
-      </c>
-      <c r="K39" t="n">
-        <v>0</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-8.07979</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-79.04604</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2497,20 +2865,30 @@
           <t>TESORITOS DE JESUS</t>
         </is>
       </c>
-      <c r="G40" t="n">
-        <v>-8.059279999999999</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-79.05502</v>
-      </c>
-      <c r="I40" t="n">
-        <v>279</v>
-      </c>
-      <c r="J40" t="n">
-        <v>17</v>
-      </c>
-      <c r="K40" t="n">
-        <v>0</v>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-8.05928</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>-79.05502</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -2549,20 +2927,30 @@
           <t>PERUANO IRLANDES</t>
         </is>
       </c>
-      <c r="G41" t="n">
-        <v>-8.08342</v>
-      </c>
-      <c r="H41" t="n">
-        <v>-79.04455</v>
-      </c>
-      <c r="I41" t="n">
-        <v>116</v>
-      </c>
-      <c r="J41" t="n">
-        <v>29</v>
-      </c>
-      <c r="K41" t="n">
-        <v>1</v>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-8.08342</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-79.04455</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2601,20 +2989,30 @@
           <t>LORD COPERNICO</t>
         </is>
       </c>
-      <c r="G42" t="n">
-        <v>-8.04792</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-79.0724</v>
-      </c>
-      <c r="I42" t="n">
-        <v>312</v>
-      </c>
-      <c r="J42" t="n">
-        <v>28</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-8.04792</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-79.0724</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2653,20 +3051,30 @@
           <t>PEREGRINO JUAN XXIII</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>-8.079029999999999</v>
-      </c>
-      <c r="H43" t="n">
-        <v>-79.04886</v>
-      </c>
-      <c r="I43" t="n">
-        <v>220</v>
-      </c>
-      <c r="J43" t="n">
-        <v>17</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-8.07903</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-79.04886</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2705,20 +3113,30 @@
           <t>MUNDO FELIZ</t>
         </is>
       </c>
-      <c r="G44" t="n">
-        <v>-8.064590000000003</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-79.07877000000001</v>
-      </c>
-      <c r="I44" t="n">
-        <v>330</v>
-      </c>
-      <c r="J44" t="n">
-        <v>19</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-8.064590000000003</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>-79.07877</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2757,20 +3175,30 @@
           <t>PAIDEIA</t>
         </is>
       </c>
-      <c r="G45" t="n">
-        <v>-8.08005</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-79.03769</v>
-      </c>
-      <c r="I45" t="n">
-        <v>375</v>
-      </c>
-      <c r="J45" t="n">
-        <v>35</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-8.08005</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-79.03769</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2809,20 +3237,30 @@
           <t>JOHANNES GUTENBERG</t>
         </is>
       </c>
-      <c r="G46" t="n">
-        <v>-8.082739999999999</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-79.04386</v>
-      </c>
-      <c r="I46" t="n">
-        <v>59</v>
-      </c>
-      <c r="J46" t="n">
-        <v>9</v>
-      </c>
-      <c r="K46" t="n">
-        <v>1</v>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-8.08274</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>-79.04386</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2861,20 +3299,30 @@
           <t>82071</t>
         </is>
       </c>
-      <c r="G47" t="n">
-        <v>-8.04668</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-79.04931000000001</v>
-      </c>
-      <c r="I47" t="n">
-        <v>1026</v>
-      </c>
-      <c r="J47" t="n">
-        <v>41</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-8.04668</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-79.04931</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2913,20 +3361,30 @@
           <t>NIÑOS TALENTOS</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>-8.06362</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-79.07935999999999</v>
-      </c>
-      <c r="I48" t="n">
-        <v>49</v>
-      </c>
-      <c r="J48" t="n">
-        <v>4</v>
-      </c>
-      <c r="K48" t="n">
-        <v>1</v>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-8.06362</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-79.07936</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2965,20 +3423,30 @@
           <t>PEQUEÑAS ALEGRIAS</t>
         </is>
       </c>
-      <c r="G49" t="n">
-        <v>-8.070449999999999</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-79.04953999999999</v>
-      </c>
-      <c r="I49" t="n">
-        <v>264</v>
-      </c>
-      <c r="J49" t="n">
-        <v>11</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0</v>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-8.07045</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-79.04954</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -3017,20 +3485,30 @@
           <t>81749 DIVINO JESUS</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>-8.069089999999999</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-79.07153</v>
-      </c>
-      <c r="I50" t="n">
-        <v>1208</v>
-      </c>
-      <c r="J50" t="n">
-        <v>62</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-8.06909</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>-79.07153</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -3069,20 +3547,30 @@
           <t>COLEGIO DE CIENCIAS ALBERT EINSTEIN</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>-8.06588</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-79.05136</v>
-      </c>
-      <c r="I51" t="n">
-        <v>812</v>
-      </c>
-      <c r="J51" t="n">
-        <v>35</v>
-      </c>
-      <c r="K51" t="n">
-        <v>3</v>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-8.06588</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-79.05136</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>812</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3121,20 +3609,30 @@
           <t>CRISTIANA JESUS EL MAESTRO</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>-8.062533999999999</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-79.052491</v>
-      </c>
-      <c r="I52" t="n">
-        <v>295</v>
-      </c>
-      <c r="J52" t="n">
-        <v>20</v>
-      </c>
-      <c r="K52" t="n">
-        <v>3</v>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-8.062534</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>-79.052491</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3173,20 +3671,30 @@
           <t>GENEVA SCHOOL - PERU MISSION CHRISTIAN MISSIONARY SOCIETY</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>-8.071343000000002</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-79.062382</v>
-      </c>
-      <c r="I53" t="n">
-        <v>267</v>
-      </c>
-      <c r="J53" t="n">
-        <v>18</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0</v>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-8.071343000000002</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>-79.062382</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -3225,20 +3733,30 @@
           <t>2312</t>
         </is>
       </c>
-      <c r="G54" t="n">
-        <v>-8.06277</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-79.07832999999999</v>
-      </c>
-      <c r="I54" t="n">
-        <v>144</v>
-      </c>
-      <c r="J54" t="n">
-        <v>9</v>
-      </c>
-      <c r="K54" t="n">
-        <v>1</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-8.06277</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-79.07833</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -3277,20 +3795,30 @@
           <t>PEQUEÑAS ALEGRIAS</t>
         </is>
       </c>
-      <c r="G55" t="n">
-        <v>-8.076964</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-79.04824499999999</v>
-      </c>
-      <c r="I55" t="n">
-        <v>132</v>
-      </c>
-      <c r="J55" t="n">
-        <v>8</v>
-      </c>
-      <c r="K55" t="n">
-        <v>1</v>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-8.076964</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>-79.048245</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-LA_ESPERANZA.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-LA_ESPERANZA.xlsx
@@ -501,32 +501,32 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>80546</t>
+          <t>253728</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>EL BUEN PASTOR</t>
+          <t>106</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-8.07824</t>
+          <t>-8.07296</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-79.04235</t>
+          <t>-79.05986</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -563,32 +563,32 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>80817</t>
+          <t>253827</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SOL NACIENTE</t>
+          <t>1682 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-8.07921</t>
+          <t>-8.060600000000003</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-79.04397</t>
+          <t>-79.0544</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>275</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>252578</t>
+          <t>253766</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>UNIVERSAL SCHOOLS</t>
+          <t>1560 JESUS NAZARENO</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-8.08584</t>
+          <t>-8.08089</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.03902</t>
+          <t>-79.04732</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>239</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,32 +687,32 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>253511</t>
+          <t>253771</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>81758 TELMO HOYLE DE LOS RIOS</t>
+          <t>1574 SANTA VERONICA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-8.0684</t>
+          <t>-8.081466000000002</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.07595</t>
+          <t>-79.05079</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>274</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>253525</t>
+          <t>658597</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>81764 LA CANTERA</t>
+          <t>PEQUEÑAS ALEGRIAS</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-8.05264</t>
+          <t>-8.07045</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.07451</t>
+          <t>-79.04954</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>264</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>253648</t>
+          <t>253790</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ABRAHAM LINCOLN</t>
+          <t>1576 JERUSALEN</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-8.049480000000003</t>
+          <t>-8.067970000000003</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.07246</t>
+          <t>-79.054</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>393</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>253728</t>
+          <t>254049</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>81763</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-8.07296</t>
+          <t>-8.061780000000002</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-79.05986</t>
+          <t>-79.04693</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>370</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,42 +935,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>253766</t>
+          <t>80817</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1560 JESUS NAZARENO</t>
+          <t>SOL NACIENTE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-8.08089</t>
+          <t>-8.07921</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.04732</t>
+          <t>-79.04397</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>253771</t>
+          <t>254431</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1574 SANTA VERONICA</t>
+          <t>TESORITOS DE JESUS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-8.081466000000002</t>
+          <t>-8.05928</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.05079</t>
+          <t>-79.05502</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>279</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>253790</t>
+          <t>512784</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1576 JERUSALEN</t>
+          <t>PEREGRINO JUAN XXIII</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-8.067970000000003</t>
+          <t>-8.07903</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.054</t>
+          <t>-79.04886</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>220</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,42 +1121,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>253813</t>
+          <t>253945</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1680 DIVINA MISERICORDIA</t>
+          <t>80039 MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-8.07512</t>
+          <t>-8.07985</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.04832</t>
+          <t>-79.04161</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>444</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1183,42 +1183,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>253827</t>
+          <t>254186</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1682 VIRGEN DE FATIMA</t>
+          <t>INDOAMERICANO</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-8.060600000000003</t>
+          <t>-8.06233</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.0544</t>
+          <t>-79.05275</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>225</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>253832</t>
+          <t>787212</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2021 SARITA COLONIA</t>
+          <t>GENEVA SCHOOL - PERU MISSION CHRISTIAN MISSIONARY SOCIETY</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-8.05533</t>
+          <t>-8.071343000000002</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-79.05322</t>
+          <t>-79.062382</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>267</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>253912</t>
+          <t>254105</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CARLOS MANUEL COX ROSSE</t>
+          <t>MADRE DE CRISTO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-8.06791</t>
+          <t>-8.08009</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.05753</t>
+          <t>-79.04522</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>525</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>253926</t>
+          <t>520722</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>80036 SAN MARTIN DE PORRES</t>
+          <t>MUNDO FELIZ</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-8.07269</t>
+          <t>-8.064590000000003</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.04401</t>
+          <t>-79.07877</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>330</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>253931</t>
+          <t>254266</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>80038 SAN FRANCISCO DE ASIS</t>
+          <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-8.06649</t>
+          <t>-8.07479208879985</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.04856</t>
+          <t>-79.0506266257255</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>329</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>253945</t>
+          <t>254271</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>80039 MIGUEL GRAU SEMINARIO</t>
+          <t>DOS DE MAYO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-8.07985</t>
+          <t>-8.08042</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-79.04161</t>
+          <t>-79.04102</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>392</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1555,42 +1555,42 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>253950</t>
+          <t>754768</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>80040 DIVINO MAESTRO</t>
+          <t>CRISTIANA JESUS EL MAESTRO</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-8.08074</t>
+          <t>-8.062534</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-79.04684</t>
+          <t>-79.052491</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>295</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>253969</t>
+          <t>254313</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>80041 JOSE CARLOS MARIATEGUI</t>
+          <t>MARIANO MELGAR</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-8.08279</t>
+          <t>-8.06734</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-79.0369</t>
+          <t>-79.0586</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>319</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>253974</t>
+          <t>254346</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>80821 CESAR VALLEJO MENDOZA</t>
+          <t>LIBERTAD</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-8.083930000000002</t>
+          <t>-8.07979</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-79.03414</t>
+          <t>-79.04604</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>408</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>253988</t>
+          <t>80546</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>80822 SANTA MARIA DE LA ESPERANZA</t>
+          <t>EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-8.0674</t>
+          <t>-8.07824</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-79.0542</t>
+          <t>-79.04235</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>360</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>23</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1803,32 +1803,32 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>253993</t>
+          <t>253648</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>80829 JOSE OLAYA</t>
+          <t>ABRAHAM LINCOLN</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-8.076700000000002</t>
+          <t>-8.049480000000003</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-79.04996</t>
+          <t>-79.07246</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>437</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -1865,32 +1865,32 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>254006</t>
+          <t>507004</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>81608 SAN JOSE</t>
+          <t>LORD COPERNICO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-8.0608</t>
+          <t>-8.04792</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-79.0551</t>
+          <t>-79.0724</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>312</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1927,42 +1927,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>254011</t>
+          <t>254445</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>81748</t>
+          <t>PERUANO IRLANDES</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-8.06773</t>
+          <t>-8.08342</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-79.06389</t>
+          <t>-79.04455</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>116</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>254030</t>
+          <t>254252</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>81751 DIOS ES AMOR</t>
+          <t>AMIGOS DE JESUS</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-8.05656</t>
+          <t>-8.0542</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-79.0531</t>
+          <t>-79.05319</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>474</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>254049</t>
+          <t>253525</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>81763</t>
+          <t>81764 LA CANTERA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-8.061780000000002</t>
+          <t>-8.05264</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-79.04693</t>
+          <t>-79.07451</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>754</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,37 +2113,37 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>254087</t>
+          <t>541550</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2028 LUCERITO DEL AMANECER</t>
+          <t>PAIDEIA</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-8.050090000000003</t>
+          <t>-8.08005</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-79.05092</t>
+          <t>-79.03769</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>375</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2175,37 +2175,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>254105</t>
+          <t>659460</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>MADRE DE CRISTO</t>
+          <t>COLEGIO DE CIENCIAS ALBERT EINSTEIN</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-8.08009</t>
+          <t>-8.06588</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-79.04522</t>
+          <t>-79.05136</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>812</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>254148</t>
+          <t>253511</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 36</t>
+          <t>81758 TELMO HOYLE DE LOS RIOS</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-8.0745</t>
+          <t>-8.0684</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-79.0618</t>
+          <t>-79.07595</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>953</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2423,42 +2423,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>254186</t>
+          <t>657456</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>INDOAMERICANO</t>
+          <t>NIÑOS TALENTOS</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-8.06233</t>
+          <t>-8.06362</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-79.05275</t>
+          <t>-79.07936</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>49</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2485,42 +2485,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>254233</t>
+          <t>254011</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ESTUDIANTES EXCELENTES</t>
+          <t>81748</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-8.06227</t>
+          <t>-8.06773</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-79.05297</t>
+          <t>-79.06389</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>840</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>254252</t>
+          <t>657164</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AMIGOS DE JESUS</t>
+          <t>82071</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-8.0542</t>
+          <t>-8.04668</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-79.05319</t>
+          <t>-79.04931</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>254266</t>
+          <t>253969</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>DANIEL ALCIDES CARRION</t>
+          <t>80041 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-8.07479208879985</t>
+          <t>-8.08279</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-79.0506266257255</t>
+          <t>-79.0369</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>254271</t>
+          <t>254030</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>DOS DE MAYO</t>
+          <t>81751 DIOS ES AMOR</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-8.08042</t>
+          <t>-8.05656</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-79.04102</t>
+          <t>-79.0531</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2733,32 +2733,32 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>254313</t>
+          <t>253912</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>MARIANO MELGAR</t>
+          <t>CARLOS MANUEL COX ROSSE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-8.06734</t>
+          <t>-8.06791</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-79.0586</t>
+          <t>-79.05753</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>254346</t>
+          <t>253931</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LIBERTAD</t>
+          <t>80038 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-8.07979</t>
+          <t>-8.06649</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-79.04604</t>
+          <t>-79.04856</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>254431</t>
+          <t>254148</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>TESORITOS DE JESUS</t>
+          <t>FE Y ALEGRIA 36</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-8.05928</t>
+          <t>-8.0745</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-79.05502</t>
+          <t>-79.0618</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2919,42 +2919,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>254445</t>
+          <t>658615</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>PERUANO IRLANDES</t>
+          <t>81749 DIVINO JESUS</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-8.08342</t>
+          <t>-8.06909</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-79.04455</t>
+          <t>-79.07153</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2981,42 +2981,42 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>507004</t>
+          <t>253950</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>LORD COPERNICO</t>
+          <t>80040 DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-8.04792</t>
+          <t>-8.08074</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-79.0724</t>
+          <t>-79.04684</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>512784</t>
+          <t>253926</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>PEREGRINO JUAN XXIII</t>
+          <t>80036 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-8.07903</t>
+          <t>-8.07269</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-79.04886</t>
+          <t>-79.04401</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>67</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>520722</t>
+          <t>254006</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>MUNDO FELIZ</t>
+          <t>81608 SAN JOSE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-8.064590000000003</t>
+          <t>-8.0608</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-79.07877</t>
+          <t>-79.0551</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3167,32 +3167,32 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>541550</t>
+          <t>252578</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>PAIDEIA</t>
+          <t>UNIVERSAL SCHOOLS</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-8.08005</t>
+          <t>-8.08584</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-79.03769</t>
+          <t>-79.03902</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>310</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -3229,32 +3229,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>575540</t>
+          <t>254087</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>JOHANNES GUTENBERG</t>
+          <t>2028 LUCERITO DEL AMANECER</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-8.08274</t>
+          <t>-8.050090000000003</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-79.04386</t>
+          <t>-79.05092</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>197</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -3291,37 +3291,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>657164</t>
+          <t>835393</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>82071</t>
+          <t>PEQUEÑAS ALEGRIAS</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-8.04668</t>
+          <t>-8.076964</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-79.04931</t>
+          <t>-79.048245</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>132</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3353,37 +3353,37 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>657456</t>
+          <t>253993</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>NIÑOS TALENTOS</t>
+          <t>80829 JOSE OLAYA</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-8.06362</t>
+          <t>-8.076700000000002</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-79.07936</t>
+          <t>-79.04996</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>81</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>658597</t>
+          <t>253988</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>PEQUEÑAS ALEGRIAS</t>
+          <t>80822 SANTA MARIA DE LA ESPERANZA</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-8.07045</t>
+          <t>-8.0674</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-79.04954</t>
+          <t>-79.0542</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>86</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>658615</t>
+          <t>253974</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>81749 DIVINO JESUS</t>
+          <t>80821 CESAR VALLEJO MENDOZA</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-8.06909</t>
+          <t>-8.083930000000002</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-79.07153</t>
+          <t>-79.03414</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3539,37 +3539,37 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>659460</t>
+          <t>253813</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>COLEGIO DE CIENCIAS ALBERT EINSTEIN</t>
+          <t>1680 DIVINA MISERICORDIA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-8.06588</t>
+          <t>-8.07512</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-79.05136</t>
+          <t>-79.04832</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>212</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3601,37 +3601,37 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>754768</t>
+          <t>253832</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>CRISTIANA JESUS EL MAESTRO</t>
+          <t>2021 SARITA COLONIA</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-8.062534</t>
+          <t>-8.05533</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-79.052491</t>
+          <t>-79.05322</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>226</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3663,37 +3663,37 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>787212</t>
+          <t>254233</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>GENEVA SCHOOL - PERU MISSION CHRISTIAN MISSIONARY SOCIETY</t>
+          <t>ESTUDIANTES EXCELENTES</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-8.071343000000002</t>
+          <t>-8.06227</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-79.062382</t>
+          <t>-79.05297</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>96</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3725,27 +3725,27 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>791638</t>
+          <t>575540</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2312</t>
+          <t>JOHANNES GUTENBERG</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-8.06277</t>
+          <t>-8.08274</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-79.07833</t>
+          <t>-79.04386</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>59</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>835393</t>
+          <t>791638</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PEQUEÑAS ALEGRIAS</t>
+          <t>2312</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-8.076964</t>
+          <t>-8.06277</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-79.048245</t>
+          <t>-79.07833</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>144</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">

--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-LA_ESPERANZA.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-LA_ESPERANZA.xlsx
@@ -573,7 +573,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-8.060600000000003</t>
+          <t>-8.0606</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -697,7 +697,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-8.081466000000002</t>
+          <t>-8.081466</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-8.067970000000003</t>
+          <t>-8.06797</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-8.061780000000002</t>
+          <t>-8.06178</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-8.071343000000002</t>
+          <t>-8.071343</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-8.064590000000003</t>
+          <t>-8.06459</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-8.049480000000003</t>
+          <t>-8.04948</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3239,7 +3239,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-8.050090000000003</t>
+          <t>-8.05009</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-8.076700000000002</t>
+          <t>-8.0767</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-8.083930000000002</t>
+          <t>-8.08393</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">

--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-LA_ESPERANZA.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-LA_ESPERANZA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>253728</t>
+          <t>835393</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>PEQUEÑAS ALEGRIAS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-8.07296</t>
+          <t>132</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-79.05986</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-8.076964</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-79.048245</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>253827</t>
+          <t>791638</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1682 VIRGEN DE FATIMA</t>
+          <t>2312</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-8.0606</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-79.0544</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>-8.06277</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-79.07833</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>253766</t>
+          <t>787212</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1560 JESUS NAZARENO</t>
+          <t>GENEVA SCHOOL - PERU MISSION CHRISTIAN MISSIONARY SOCIETY</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-8.08089</t>
+          <t>267</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-79.04732</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>239</t>
+          <t>-8.071343000000002</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-79.062382</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>253771</t>
+          <t>754768</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1574 SANTA VERONICA</t>
+          <t>CRISTIANA JESUS EL MAESTRO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-8.081466</t>
+          <t>295</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-79.05079</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>-8.062534</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-79.052491</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,37 +749,37 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>658597</t>
+          <t>659460</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PEQUEÑAS ALEGRIAS</t>
+          <t>COLEGIO DE CIENCIAS ALBERT EINSTEIN</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-8.07045</t>
+          <t>812</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-79.04954</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>264</t>
+          <t>-8.06588</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>-79.05136</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>253790</t>
+          <t>658615</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1576 JERUSALEN</t>
+          <t>81749 DIVINO JESUS</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-8.06797</t>
+          <t>1208</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-79.054</t>
+          <t>62</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>393</t>
+          <t>-8.06909</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>-79.07153</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>254049</t>
+          <t>658597</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>81763</t>
+          <t>PEQUEÑAS ALEGRIAS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-8.06178</t>
+          <t>264</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-79.04693</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>-8.07045</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>-79.04954</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,42 +935,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>80817</t>
+          <t>657456</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SOL NACIENTE</t>
+          <t>NIÑOS TALENTOS</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-8.07921</t>
+          <t>49</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-79.04397</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>-8.06362</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-79.07936</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>254431</t>
+          <t>657164</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>TESORITOS DE JESUS</t>
+          <t>82071</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-8.05928</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-79.05502</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>-8.04668</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-79.04931</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,37 +1059,37 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>512784</t>
+          <t>575540</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PEREGRINO JUAN XXIII</t>
+          <t>JOHANNES GUTENBERG</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-8.07903</t>
+          <t>59</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-79.04886</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>-8.08274</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>-79.04386</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>253945</t>
+          <t>541550</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>80039 MIGUEL GRAU SEMINARIO</t>
+          <t>PAIDEIA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-8.07985</t>
+          <t>375</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-79.04161</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>-8.08005</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-79.03769</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1183,42 +1183,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>254186</t>
+          <t>520722</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>INDOAMERICANO</t>
+          <t>MUNDO FELIZ</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-8.06233</t>
+          <t>330</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-79.05275</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>225</t>
+          <t>-8.064590000000003</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-79.07877</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>787212</t>
+          <t>512784</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>GENEVA SCHOOL - PERU MISSION CHRISTIAN MISSIONARY SOCIETY</t>
+          <t>PEREGRINO JUAN XXIII</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-8.071343</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-79.062382</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>-8.07903</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-79.04886</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>254105</t>
+          <t>507004</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>MADRE DE CRISTO</t>
+          <t>LORD COPERNICO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-8.08009</t>
+          <t>312</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-79.04522</t>
+          <t>28</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>-8.04792</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-79.0724</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,37 +1369,37 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>520722</t>
+          <t>254445</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>MUNDO FELIZ</t>
+          <t>PERUANO IRLANDES</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-8.06459</t>
+          <t>116</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-79.07877</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>-8.08342</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-79.04455</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>254266</t>
+          <t>254431</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>DANIEL ALCIDES CARRION</t>
+          <t>TESORITOS DE JESUS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-8.07479208879985</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-79.0506266257255</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>-8.05928</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-79.05502</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>254271</t>
+          <t>254346</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DOS DE MAYO</t>
+          <t>LIBERTAD</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-8.08042</t>
+          <t>408</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-79.04102</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>-8.07979</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-79.04604</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,37 +1555,37 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>754768</t>
+          <t>254313</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CRISTIANA JESUS EL MAESTRO</t>
+          <t>MARIANO MELGAR</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-8.062534</t>
+          <t>319</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-79.052491</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>-8.06734</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>-79.0586</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1617,32 +1617,32 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>254313</t>
+          <t>254271</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>MARIANO MELGAR</t>
+          <t>DOS DE MAYO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-8.06734</t>
+          <t>392</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-79.0586</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>-8.08042</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>-79.04102</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>254346</t>
+          <t>254266</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>LIBERTAD</t>
+          <t>DANIEL ALCIDES CARRION</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-8.07979</t>
+          <t>329</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-79.04604</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>-8.07479208879985</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>-79.0506266257255</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1741,32 +1741,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>80546</t>
+          <t>254252</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>EL BUEN PASTOR</t>
+          <t>AMIGOS DE JESUS</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-8.07824</t>
+          <t>474</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-79.04235</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>-8.0542</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-79.05319</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1803,37 +1803,37 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>253648</t>
+          <t>254233</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>ABRAHAM LINCOLN</t>
+          <t>ESTUDIANTES EXCELENTES</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-8.04948</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-79.07246</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>437</t>
+          <t>-8.06227</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-79.05297</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1865,42 +1865,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>507004</t>
+          <t>254186</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>LORD COPERNICO</t>
+          <t>INDOAMERICANO</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-8.04792</t>
+          <t>225</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-79.0724</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>-8.06233</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>-79.05275</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1927,37 +1927,37 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>254445</t>
+          <t>254148</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PERUANO IRLANDES</t>
+          <t>FE Y ALEGRIA 36</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-8.08342</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-79.04455</t>
+          <t>61</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>-8.0745</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>-79.0618</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1989,32 +1989,32 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>254252</t>
+          <t>254129</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AMIGOS DE JESUS</t>
+          <t>CRISTO REY</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-8.0542</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-79.05319</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>474</t>
+          <t>-8.07098</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>-79.05023</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2051,32 +2051,32 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>253525</t>
+          <t>254110</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>81764 LA CANTERA</t>
+          <t>1702 SANTISIMO SACRAMENTO</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-8.05264</t>
+          <t>698</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-79.07451</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>754</t>
+          <t>-8.08329</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-79.03653</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -2113,32 +2113,32 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>541550</t>
+          <t>254105</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PAIDEIA</t>
+          <t>MADRE DE CRISTO</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-8.08005</t>
+          <t>525</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-79.03769</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>-8.08009</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-79.04522</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2175,37 +2175,37 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>659460</t>
+          <t>254087</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>COLEGIO DE CIENCIAS ALBERT EINSTEIN</t>
+          <t>2028 LUCERITO DEL AMANECER</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-8.06588</t>
+          <t>197</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-79.05136</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>812</t>
+          <t>-8.050090000000003</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-79.05092</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>254110</t>
+          <t>254049</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1702 SANTISIMO SACRAMENTO</t>
+          <t>81763</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-8.08329</t>
+          <t>370</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-79.03653</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>698</t>
+          <t>-8.061780000000002</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-79.04693</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2299,32 +2299,32 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>254129</t>
+          <t>254030</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>CRISTO REY</t>
+          <t>81751 DIOS ES AMOR</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-8.07098</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-79.05023</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>-8.05656</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-79.0531</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2361,32 +2361,32 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>253511</t>
+          <t>254011</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>81758 TELMO HOYLE DE LOS RIOS</t>
+          <t>81748</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-8.0684</t>
+          <t>840</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-79.07595</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>-8.06773</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>-79.06389</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2423,42 +2423,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>657456</t>
+          <t>254006</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NIÑOS TALENTOS</t>
+          <t>81608 SAN JOSE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-8.06362</t>
+          <t>1801</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-79.07936</t>
+          <t>68</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>-8.0608</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-79.0551</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2485,32 +2485,32 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>254011</t>
+          <t>253993</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>81748</t>
+          <t>80829 JOSE OLAYA</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-8.06773</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>-79.06389</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>-8.076700000000002</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-79.04996</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2547,32 +2547,32 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>657164</t>
+          <t>253988</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>82071</t>
+          <t>80822 SANTA MARIA DE LA ESPERANZA</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-8.04668</t>
+          <t>2138</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-79.04931</t>
+          <t>86</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>-8.0674</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-79.0542</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2609,32 +2609,32 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>253969</t>
+          <t>253974</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>80041 JOSE CARLOS MARIATEGUI</t>
+          <t>80821 CESAR VALLEJO MENDOZA</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-8.08279</t>
+          <t>1765</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-79.0369</t>
+          <t>88</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1059</t>
+          <t>-8.083930000000002</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>-79.03414</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -2671,32 +2671,32 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>254030</t>
+          <t>253969</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>81751 DIOS ES AMOR</t>
+          <t>80041 JOSE CARLOS MARIATEGUI</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-8.05656</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-79.0531</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>-8.08279</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>-79.0369</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -2733,37 +2733,37 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>253912</t>
+          <t>253950</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CARLOS MANUEL COX ROSSE</t>
+          <t>80040 DIVINO MAESTRO</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-8.06791</t>
+          <t>1590</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-79.05753</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1241</t>
+          <t>-8.08074</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-79.04684</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2795,32 +2795,32 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>253931</t>
+          <t>253945</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>80038 SAN FRANCISCO DE ASIS</t>
+          <t>80039 MIGUEL GRAU SEMINARIO</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-8.06649</t>
+          <t>444</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>-79.04856</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>-8.07985</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-79.04161</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -2857,32 +2857,32 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>254148</t>
+          <t>253931</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FE Y ALEGRIA 36</t>
+          <t>80038 SAN FRANCISCO DE ASIS</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-8.0745</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>-79.0618</t>
+          <t>59</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>-8.06649</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>-79.04856</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
@@ -2892,7 +2892,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2919,32 +2919,32 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>658615</t>
+          <t>253926</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>81749 DIVINO JESUS</t>
+          <t>80036 SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-8.06909</t>
+          <t>1367</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-79.07153</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>-8.07269</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>-79.04401</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2981,37 +2981,37 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>253950</t>
+          <t>253912</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>80040 DIVINO MAESTRO</t>
+          <t>CARLOS MANUEL COX ROSSE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-8.08074</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-79.04684</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1590</t>
+          <t>-8.06791</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-79.05753</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3043,32 +3043,32 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>253926</t>
+          <t>253832</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>80036 SAN MARTIN DE PORRES</t>
+          <t>2021 SARITA COLONIA</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-8.07269</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-79.04401</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1367</t>
+          <t>-8.05533</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>-79.05322</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3105,32 +3105,32 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>254006</t>
+          <t>253827</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>81608 SAN JOSE</t>
+          <t>1682 VIRGEN DE FATIMA</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-8.0608</t>
+          <t>275</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-79.0551</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>-8.060600000000003</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>-79.0544</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3167,37 +3167,37 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>252578</t>
+          <t>253813</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>UNIVERSAL SCHOOLS</t>
+          <t>1680 DIVINA MISERICORDIA</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-8.08584</t>
+          <t>212</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-79.03902</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>-8.07512</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-79.04832</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3229,37 +3229,37 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>254087</t>
+          <t>253790</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2028 LUCERITO DEL AMANECER</t>
+          <t>1576 JERUSALEN</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-8.05009</t>
+          <t>393</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-79.05092</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>-8.067970000000003</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>-79.054</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3291,37 +3291,37 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>835393</t>
+          <t>253771</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>PEQUEÑAS ALEGRIAS</t>
+          <t>1574 SANTA VERONICA</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-8.076964</t>
+          <t>274</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>-79.048245</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>-8.081466000000002</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>-79.05079</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3353,37 +3353,37 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>253993</t>
+          <t>253766</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>80829 JOSE OLAYA</t>
+          <t>1560 JESUS NAZARENO</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-8.0767</t>
+          <t>239</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>-79.04996</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>-8.08089</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>-79.04732</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3415,32 +3415,32 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>253988</t>
+          <t>253728</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>80822 SANTA MARIA DE LA ESPERANZA</t>
+          <t>106</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-8.0674</t>
+          <t>226</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>-79.0542</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2138</t>
+          <t>-8.07296</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>-79.05986</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3477,32 +3477,32 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>253974</t>
+          <t>253648</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>80821 CESAR VALLEJO MENDOZA</t>
+          <t>ABRAHAM LINCOLN</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-8.08393</t>
+          <t>437</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>-79.03414</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>1765</t>
+          <t>-8.049480000000003</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>-79.07246</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3539,37 +3539,37 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>253813</t>
+          <t>253525</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1680 DIVINA MISERICORDIA</t>
+          <t>81764 LA CANTERA</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-8.07512</t>
+          <t>754</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>-79.04832</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>-8.05264</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-79.07451</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>253832</t>
+          <t>253511</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2021 SARITA COLONIA</t>
+          <t>81758 TELMO HOYLE DE LOS RIOS</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-8.05533</t>
+          <t>953</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>-79.05322</t>
+          <t>38</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>-8.0684</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-79.07595</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -3663,37 +3663,37 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>254233</t>
+          <t>252578</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>ESTUDIANTES EXCELENTES</t>
+          <t>UNIVERSAL SCHOOLS</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-8.06227</t>
+          <t>310</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>-79.05297</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>-8.08584</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-79.03902</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3725,42 +3725,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>575540</t>
+          <t>080817</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>JOHANNES GUTENBERG</t>
+          <t>SOL NACIENTE</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-8.08274</t>
+          <t>360</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>-79.04386</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>-8.07921</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-79.04397</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -3787,42 +3787,42 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>791638</t>
+          <t>080546</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2312</t>
+          <t>EL BUEN PASTOR</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-8.06277</t>
+          <t>360</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>-79.07833</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>-8.07824</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>-79.04235</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-LA_ESPERANZA.xlsx
+++ b/ZonasEscolares/excels/LA_LIBERTAD-TRUJILLO-LA_ESPERANZA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
